--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,60 +780,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R3" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +851,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,63 +869,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702610</v>
+        <v>127704994</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495089</v>
+        <v>494916</v>
       </c>
       <c r="R4" t="n">
-        <v>6720547</v>
+        <v>6720685</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,9 +961,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,12 +989,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,46 +1111,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702557</v>
+        <v>127702618</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495092</v>
+        <v>495091</v>
       </c>
       <c r="R6" t="n">
-        <v>6720647</v>
+        <v>6720516</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1221,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702451</v>
+        <v>127702677</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>56855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,31 +1223,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494955</v>
+        <v>495011</v>
       </c>
       <c r="R7" t="n">
-        <v>6720654</v>
+        <v>6720464</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,42 +1317,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702677</v>
+        <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>56853</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495011</v>
+        <v>495092</v>
       </c>
       <c r="R8" t="n">
-        <v>6720464</v>
+        <v>6720647</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1414,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1432,37 +1427,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702618</v>
+        <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>98370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495091</v>
+        <v>494955</v>
       </c>
       <c r="R9" t="n">
-        <v>6720516</v>
+        <v>6720654</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>127702600</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127702589</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,46 +2161,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702501</v>
+        <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>56853</v>
+        <v>91628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495076</v>
+        <v>494992</v>
       </c>
       <c r="R16" t="n">
-        <v>6720763</v>
+        <v>6720453</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2252,6 +2247,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2270,41 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702771</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91626</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494992</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720453</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>127705132</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702953</v>
+        <v>127702821</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,28 +2506,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2537,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494954</v>
+        <v>494992</v>
       </c>
       <c r="R19" t="n">
-        <v>6720410</v>
+        <v>6720444</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2600,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127702821</v>
+        <v>127702953</v>
       </c>
       <c r="B20" t="n">
-        <v>91330</v>
+        <v>91352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,24 +2607,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494992</v>
+        <v>494954</v>
       </c>
       <c r="R20" t="n">
-        <v>6720444</v>
+        <v>6720410</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2701,46 +2701,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2748,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R21" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2811,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702866</v>
+        <v>127702660</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,26 +2813,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2849,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495000</v>
+        <v>495027</v>
       </c>
       <c r="R22" t="n">
-        <v>6720439</v>
+        <v>6720505</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2893,7 +2889,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2915,7 +2910,7 @@
         <v>127702665</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,42 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702660</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3065,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495027</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720505</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3109,6 +3108,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,60 +3338,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127704897</v>
+        <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494861</v>
+        <v>495079</v>
       </c>
       <c r="R27" t="n">
-        <v>6720679</v>
+        <v>6720624</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3418,19 +3409,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,22 +3427,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127705446</v>
+        <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,7 +3469,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3501,17 +3482,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494939</v>
+        <v>494878</v>
       </c>
       <c r="R28" t="n">
-        <v>6720421</v>
+        <v>6720648</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3538,19 +3519,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3566,63 +3537,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127702579</v>
+        <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495079</v>
+        <v>494861</v>
       </c>
       <c r="R29" t="n">
-        <v>6720624</v>
+        <v>6720679</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3649,9 +3629,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3667,22 +3657,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127702385</v>
+        <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3709,7 +3699,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3722,17 +3712,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494878</v>
+        <v>494939</v>
       </c>
       <c r="R30" t="n">
-        <v>6720648</v>
+        <v>6720421</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,9 +3749,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,22 +3777,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>56855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,30 +3800,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3833,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R31" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3877,7 +3876,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3899,7 +3897,7 @@
         <v>127702791</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,29 +4015,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4049,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R33" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4093,6 +4092,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>127702940</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127702380</v>
+        <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91295</v>
+        <v>91332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494869</v>
+        <v>494927</v>
       </c>
       <c r="R39" t="n">
-        <v>6720629</v>
+        <v>6720666</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4758,46 +4758,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127702522</v>
+        <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>91297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4805,10 +4796,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495097</v>
+        <v>494869</v>
       </c>
       <c r="R40" t="n">
-        <v>6720656</v>
+        <v>6720629</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4868,37 +4859,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127702407</v>
+        <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494927</v>
+        <v>495097</v>
       </c>
       <c r="R41" t="n">
-        <v>6720666</v>
+        <v>6720656</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -881,7 +881,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704994</v>
+        <v>127702569</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -911,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -924,17 +924,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494916</v>
+        <v>495103</v>
       </c>
       <c r="R4" t="n">
-        <v>6720685</v>
+        <v>6720644</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +961,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,19 +979,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702569</v>
+        <v>127704994</v>
       </c>
       <c r="B5" t="n">
         <v>98450</v>
@@ -1031,7 +1021,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1044,17 +1034,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495103</v>
+        <v>494916</v>
       </c>
       <c r="R5" t="n">
-        <v>6720644</v>
+        <v>6720685</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1071,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,49 +1099,54 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702618</v>
+        <v>127702677</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495091</v>
+        <v>495011</v>
       </c>
       <c r="R6" t="n">
-        <v>6720516</v>
+        <v>6720464</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1193,7 +1198,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702677</v>
+        <v>127702451</v>
       </c>
       <c r="B7" t="n">
-        <v>56855</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,31 +1227,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495011</v>
+        <v>494955</v>
       </c>
       <c r="R7" t="n">
-        <v>6720464</v>
+        <v>6720654</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1299,6 +1303,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,46 +1322,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702557</v>
+        <v>127702618</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495092</v>
+        <v>495091</v>
       </c>
       <c r="R8" t="n">
-        <v>6720647</v>
+        <v>6720516</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1427,38 +1423,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702451</v>
+        <v>127702557</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494955</v>
+        <v>495092</v>
       </c>
       <c r="R9" t="n">
-        <v>6720654</v>
+        <v>6720647</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -2060,37 +2060,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B15" t="n">
-        <v>91628</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2142,7 +2151,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2161,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702771</v>
+        <v>127702962</v>
       </c>
       <c r="B16" t="n">
         <v>91628</v>
@@ -2189,11 +2197,7 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494992</v>
+        <v>494952</v>
       </c>
       <c r="R16" t="n">
-        <v>6720453</v>
+        <v>6720405</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2266,46 +2270,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702771</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>91628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>494992</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720453</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2356,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127705132</v>
+        <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,45 +2386,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495088</v>
+        <v>494992</v>
       </c>
       <c r="R18" t="n">
-        <v>6720826</v>
+        <v>6720444</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,54 +2446,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702821</v>
+        <v>127705132</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,40 +2487,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494992</v>
+        <v>495088</v>
       </c>
       <c r="R19" t="n">
-        <v>6720444</v>
+        <v>6720826</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2566,30 +2552,44 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702660</v>
+        <v>127702665</v>
       </c>
       <c r="B22" t="n">
         <v>57660</v>
@@ -2835,7 +2835,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495027</v>
+        <v>495093</v>
       </c>
       <c r="R22" t="n">
-        <v>6720505</v>
+        <v>6720523</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2881,6 +2881,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702665</v>
+        <v>127702660</v>
       </c>
       <c r="B23" t="n">
         <v>57660</v>
@@ -2940,7 +2945,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495093</v>
+        <v>495027</v>
       </c>
       <c r="R23" t="n">
-        <v>6720523</v>
+        <v>6720505</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2986,11 +2991,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3894,40 +3894,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702791</v>
+        <v>127702400</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3937,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495005</v>
+        <v>494929</v>
       </c>
       <c r="R32" t="n">
-        <v>6720454</v>
+        <v>6720649</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3975,17 +3976,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4004,41 +4001,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702400</v>
+        <v>127702791</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4048,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494929</v>
+        <v>495005</v>
       </c>
       <c r="R33" t="n">
-        <v>6720649</v>
+        <v>6720454</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4086,13 +4082,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -1111,42 +1111,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702677</v>
+        <v>127702618</v>
       </c>
       <c r="B6" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495011</v>
+        <v>495091</v>
       </c>
       <c r="R6" t="n">
-        <v>6720464</v>
+        <v>6720516</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,6 +1193,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702451</v>
+        <v>127702677</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>56855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,31 +1223,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494955</v>
+        <v>495011</v>
       </c>
       <c r="R7" t="n">
-        <v>6720654</v>
+        <v>6720464</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1303,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,37 +1317,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702618</v>
+        <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1360,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495091</v>
+        <v>495092</v>
       </c>
       <c r="R8" t="n">
-        <v>6720516</v>
+        <v>6720647</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1423,42 +1427,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702557</v>
+        <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495092</v>
+        <v>494955</v>
       </c>
       <c r="R9" t="n">
-        <v>6720647</v>
+        <v>6720654</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127705132</v>
+        <v>127702953</v>
       </c>
       <c r="B19" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,45 +2487,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495088</v>
+        <v>494954</v>
       </c>
       <c r="R19" t="n">
-        <v>6720826</v>
+        <v>6720410</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2552,54 +2551,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,44 +2592,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R20" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,30 +2657,44 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3338,37 +3338,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702579</v>
+        <v>127702385</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3376,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495079</v>
+        <v>494878</v>
       </c>
       <c r="R27" t="n">
-        <v>6720624</v>
+        <v>6720648</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3439,7 +3448,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127702385</v>
+        <v>127705446</v>
       </c>
       <c r="B28" t="n">
         <v>98450</v>
@@ -3469,7 +3478,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3482,17 +3491,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494878</v>
+        <v>494939</v>
       </c>
       <c r="R28" t="n">
-        <v>6720648</v>
+        <v>6720421</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3519,9 +3528,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,72 +3556,63 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127704897</v>
+        <v>127702579</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494861</v>
+        <v>495079</v>
       </c>
       <c r="R29" t="n">
-        <v>6720679</v>
+        <v>6720624</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3629,19 +3639,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3657,19 +3657,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127705446</v>
+        <v>127704897</v>
       </c>
       <c r="B30" t="n">
         <v>98450</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494939</v>
+        <v>494861</v>
       </c>
       <c r="R30" t="n">
-        <v>6720421</v>
+        <v>6720679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,60 +4322,55 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>92634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R36" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4402,24 +4397,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,67 +4415,72 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R37" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4522,9 +4507,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -881,7 +881,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702569</v>
+        <v>127704994</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -911,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -924,17 +924,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495103</v>
+        <v>494916</v>
       </c>
       <c r="R4" t="n">
-        <v>6720644</v>
+        <v>6720685</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,9 +961,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,19 +989,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127704994</v>
+        <v>127702569</v>
       </c>
       <c r="B5" t="n">
         <v>98450</v>
@@ -1021,7 +1031,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1034,17 +1044,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494916</v>
+        <v>495103</v>
       </c>
       <c r="R5" t="n">
-        <v>6720685</v>
+        <v>6720644</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1081,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,49 +1099,54 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702618</v>
+        <v>127702677</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495091</v>
+        <v>495011</v>
       </c>
       <c r="R6" t="n">
-        <v>6720516</v>
+        <v>6720464</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1193,7 +1198,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,42 +1216,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702677</v>
+        <v>127702618</v>
       </c>
       <c r="B7" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495011</v>
+        <v>495091</v>
       </c>
       <c r="R7" t="n">
-        <v>6720464</v>
+        <v>6720516</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1299,6 +1298,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2060,46 +2060,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702501</v>
+        <v>127702771</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>91628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495076</v>
+        <v>494992</v>
       </c>
       <c r="R15" t="n">
-        <v>6720763</v>
+        <v>6720453</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2151,6 +2146,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2270,41 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702771</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91628</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494992</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720453</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702665</v>
+        <v>127702660</v>
       </c>
       <c r="B22" t="n">
         <v>57660</v>
@@ -2835,7 +2835,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495093</v>
+        <v>495027</v>
       </c>
       <c r="R22" t="n">
-        <v>6720523</v>
+        <v>6720505</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2881,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,42 +2907,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702660</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2955,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495027</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720505</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2999,6 +2998,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,46 +3017,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702665</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495093</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720523</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3102,13 +3098,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3127,37 +3127,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127703242</v>
+        <v>127702373</v>
       </c>
       <c r="B25" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3165,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494910</v>
+        <v>494858</v>
       </c>
       <c r="R25" t="n">
-        <v>6720386</v>
+        <v>6720620</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3228,46 +3237,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127702373</v>
+        <v>127703242</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494858</v>
+        <v>494910</v>
       </c>
       <c r="R26" t="n">
-        <v>6720620</v>
+        <v>6720386</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3338,46 +3338,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702385</v>
+        <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3385,10 +3376,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494878</v>
+        <v>495079</v>
       </c>
       <c r="R27" t="n">
-        <v>6720648</v>
+        <v>6720624</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3448,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127705446</v>
+        <v>127702385</v>
       </c>
       <c r="B28" t="n">
         <v>98450</v>
@@ -3478,7 +3469,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3491,17 +3482,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494939</v>
+        <v>494878</v>
       </c>
       <c r="R28" t="n">
-        <v>6720421</v>
+        <v>6720648</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3528,19 +3519,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3556,63 +3537,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127702579</v>
+        <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495079</v>
+        <v>494861</v>
       </c>
       <c r="R29" t="n">
-        <v>6720624</v>
+        <v>6720679</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,9 +3629,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3657,19 +3657,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127704897</v>
+        <v>127705446</v>
       </c>
       <c r="B30" t="n">
         <v>98450</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494861</v>
+        <v>494939</v>
       </c>
       <c r="R30" t="n">
-        <v>6720679</v>
+        <v>6720421</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3789,32 +3789,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702638</v>
+        <v>127702791</v>
       </c>
       <c r="B31" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3822,7 +3822,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495058</v>
+        <v>495005</v>
       </c>
       <c r="R31" t="n">
-        <v>6720525</v>
+        <v>6720454</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3868,6 +3868,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>56855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3905,30 +3910,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3938,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R32" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3982,7 +3986,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4001,40 +4004,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702791</v>
+        <v>127702400</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4044,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495005</v>
+        <v>494929</v>
       </c>
       <c r="R33" t="n">
-        <v>6720454</v>
+        <v>6720649</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4082,17 +4086,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4111,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127703223</v>
+        <v>127702940</v>
       </c>
       <c r="B34" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4122,26 +4122,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4149,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494911</v>
+        <v>494952</v>
       </c>
       <c r="R34" t="n">
-        <v>6720390</v>
+        <v>6720414</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4179,12 +4184,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4193,7 +4203,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4212,10 +4221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127702940</v>
+        <v>127703223</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4223,31 +4232,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4255,10 +4259,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494952</v>
+        <v>494911</v>
       </c>
       <c r="R35" t="n">
-        <v>6720414</v>
+        <v>6720390</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4285,17 +4289,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,6 +4303,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4322,55 +4322,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>92634</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R36" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4397,9 +4402,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,72 +4435,67 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>92634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R37" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4507,24 +4522,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,37 +780,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702610</v>
+        <v>127702569</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -818,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495089</v>
+        <v>495103</v>
       </c>
       <c r="R3" t="n">
-        <v>6720547</v>
+        <v>6720644</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,60 +890,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R4" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +961,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702569</v>
+        <v>127704994</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,7 +1021,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1044,17 +1034,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495103</v>
+        <v>494916</v>
       </c>
       <c r="R5" t="n">
-        <v>6720644</v>
+        <v>6720685</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1071,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,54 +1099,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702677</v>
+        <v>127702618</v>
       </c>
       <c r="B6" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495011</v>
+        <v>495091</v>
       </c>
       <c r="R6" t="n">
-        <v>6720464</v>
+        <v>6720516</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,6 +1193,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,37 +1212,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702618</v>
+        <v>127702677</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495091</v>
+        <v>495011</v>
       </c>
       <c r="R7" t="n">
-        <v>6720516</v>
+        <v>6720464</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1298,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,42 +1638,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1723,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1748,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,13 +1829,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2060,41 +2060,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702771</v>
+        <v>127702501</v>
       </c>
       <c r="B15" t="n">
-        <v>91628</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2102,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494992</v>
+        <v>495076</v>
       </c>
       <c r="R15" t="n">
-        <v>6720453</v>
+        <v>6720763</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2146,7 +2151,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2165,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702962</v>
+        <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2197,11 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494952</v>
+        <v>494992</v>
       </c>
       <c r="R16" t="n">
-        <v>6720405</v>
+        <v>6720453</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2266,46 +2274,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>91634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2356,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127702821</v>
+        <v>127705132</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,40 +2386,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494992</v>
+        <v>495088</v>
       </c>
       <c r="R18" t="n">
-        <v>6720444</v>
+        <v>6720826</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,40 +2451,54 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702953</v>
+        <v>127702821</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>91338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,28 +2506,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2518,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494954</v>
+        <v>494992</v>
       </c>
       <c r="R19" t="n">
-        <v>6720410</v>
+        <v>6720444</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2581,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127705132</v>
+        <v>127702953</v>
       </c>
       <c r="B20" t="n">
-        <v>57660</v>
+        <v>91358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,45 +2607,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495088</v>
+        <v>494954</v>
       </c>
       <c r="R20" t="n">
-        <v>6720826</v>
+        <v>6720410</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,44 +2671,30 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,46 +2907,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127702665</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2954,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495093</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720523</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2992,13 +2988,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,42 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702665</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3060,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495093</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720523</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3098,17 +3102,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3127,46 +3127,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127702373</v>
+        <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>91634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3174,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494858</v>
+        <v>494910</v>
       </c>
       <c r="R25" t="n">
-        <v>6720620</v>
+        <v>6720386</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3237,37 +3228,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127703242</v>
+        <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>91628</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494910</v>
+        <v>494858</v>
       </c>
       <c r="R26" t="n">
-        <v>6720386</v>
+        <v>6720620</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3442,7 +3442,7 @@
         <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>127703223</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,46 +780,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702569</v>
+        <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495103</v>
+        <v>495089</v>
       </c>
       <c r="R3" t="n">
-        <v>6720644</v>
+        <v>6720547</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -890,37 +881,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702610</v>
+        <v>127702569</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495089</v>
+        <v>495103</v>
       </c>
       <c r="R4" t="n">
-        <v>6720547</v>
+        <v>6720644</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,7 +994,7 @@
         <v>127704994</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>127702618</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>127702677</v>
       </c>
       <c r="B7" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>127702600</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127702589</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,46 +2060,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>91637</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2151,6 +2142,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2172,7 +2164,7 @@
         <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,37 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91634</v>
+        <v>56858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127705132</v>
+        <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>91341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,45 +2386,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495088</v>
+        <v>494992</v>
       </c>
       <c r="R18" t="n">
-        <v>6720826</v>
+        <v>6720444</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,54 +2446,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702821</v>
+        <v>127702953</v>
       </c>
       <c r="B19" t="n">
-        <v>91338</v>
+        <v>91361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,24 +2487,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2533,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494992</v>
+        <v>494954</v>
       </c>
       <c r="R19" t="n">
-        <v>6720444</v>
+        <v>6720410</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2596,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B20" t="n">
-        <v>91358</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,44 +2592,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R20" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,30 +2657,44 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702660</v>
+        <v>127702665</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495027</v>
+        <v>495093</v>
       </c>
       <c r="R22" t="n">
-        <v>6720505</v>
+        <v>6720523</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2881,6 +2881,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702665</v>
+        <v>127702660</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2945,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495093</v>
+        <v>495027</v>
       </c>
       <c r="R23" t="n">
-        <v>6720523</v>
+        <v>6720505</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2986,11 +2991,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3020,7 +3020,7 @@
         <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,37 +3338,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702579</v>
+        <v>127702385</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3376,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495079</v>
+        <v>494878</v>
       </c>
       <c r="R27" t="n">
-        <v>6720624</v>
+        <v>6720648</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3439,10 +3448,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127702385</v>
+        <v>127704897</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3478,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3482,17 +3491,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494878</v>
+        <v>494861</v>
       </c>
       <c r="R28" t="n">
-        <v>6720648</v>
+        <v>6720679</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3519,9 +3528,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,22 +3556,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127704897</v>
+        <v>127705446</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3579,7 +3598,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3596,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494861</v>
+        <v>494939</v>
       </c>
       <c r="R29" t="n">
-        <v>6720679</v>
+        <v>6720421</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3641,7 +3660,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,60 +3688,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127705446</v>
+        <v>127702579</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494939</v>
+        <v>495079</v>
       </c>
       <c r="R30" t="n">
-        <v>6720421</v>
+        <v>6720624</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,19 +3759,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3792,7 +3792,7 @@
         <v>127702791</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127702638</v>
       </c>
       <c r="B32" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>127702940</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>127703223</v>
       </c>
       <c r="B35" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,51 +780,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702610</v>
+        <v>127704994</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495089</v>
+        <v>494916</v>
       </c>
       <c r="R3" t="n">
-        <v>6720547</v>
+        <v>6720685</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,9 +860,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,12 +888,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -884,7 +903,7 @@
         <v>127702569</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,60 +1010,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R5" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1081,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,12 +1099,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
         <v>127702618</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>127702677</v>
       </c>
       <c r="B7" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,42 +1638,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1723,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1748,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,13 +1829,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702600</v>
+        <v>127702589</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495093</v>
+        <v>495018</v>
       </c>
       <c r="R13" t="n">
-        <v>6720552</v>
+        <v>6720585</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702589</v>
+        <v>127702600</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495018</v>
+        <v>495093</v>
       </c>
       <c r="R14" t="n">
-        <v>6720585</v>
+        <v>6720552</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702771</v>
       </c>
       <c r="B15" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,11 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2098,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>494992</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720453</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702771</v>
+        <v>127702962</v>
       </c>
       <c r="B16" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,11 +2193,7 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494992</v>
+        <v>494952</v>
       </c>
       <c r="R16" t="n">
-        <v>6720453</v>
+        <v>6720405</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2269,7 +2269,7 @@
         <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127702953</v>
       </c>
       <c r="B19" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>127705132</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702866</v>
+        <v>127702660</v>
       </c>
       <c r="B21" t="n">
-        <v>91341</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,26 +2712,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495000</v>
+        <v>495027</v>
       </c>
       <c r="R21" t="n">
-        <v>6720439</v>
+        <v>6720505</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2783,7 +2788,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2809,7 @@
         <v>127702665</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,42 +2916,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702660</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2955,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495027</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720505</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2999,6 +3007,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,46 +3026,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3130,7 +3130,7 @@
         <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,46 +3338,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702385</v>
+        <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3385,10 +3376,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494878</v>
+        <v>495079</v>
       </c>
       <c r="R27" t="n">
-        <v>6720648</v>
+        <v>6720624</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3448,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127704897</v>
+        <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,7 +3469,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3491,17 +3482,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494861</v>
+        <v>494878</v>
       </c>
       <c r="R28" t="n">
-        <v>6720679</v>
+        <v>6720648</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3528,19 +3519,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3556,22 +3537,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127705446</v>
+        <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3579,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3615,10 +3596,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494939</v>
+        <v>494861</v>
       </c>
       <c r="R29" t="n">
-        <v>6720421</v>
+        <v>6720679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,7 +3631,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3660,7 +3641,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,51 +3669,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127702579</v>
+        <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495079</v>
+        <v>494939</v>
       </c>
       <c r="R30" t="n">
-        <v>6720624</v>
+        <v>6720421</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,9 +3749,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3792,7 +3792,7 @@
         <v>127702791</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127702638</v>
       </c>
       <c r="B32" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4111,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127702940</v>
+        <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4122,31 +4122,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494952</v>
+        <v>494911</v>
       </c>
       <c r="R34" t="n">
-        <v>6720414</v>
+        <v>6720390</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4184,17 +4179,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,6 +4193,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4221,10 +4212,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127703223</v>
+        <v>127702940</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,26 +4223,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4259,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494911</v>
+        <v>494952</v>
       </c>
       <c r="R35" t="n">
-        <v>6720390</v>
+        <v>6720414</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4289,12 +4285,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4322,60 +4322,55 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>92651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R36" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4402,24 +4397,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,67 +4415,72 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B37" t="n">
-        <v>92643</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R37" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4522,9 +4507,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,60 +780,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R3" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +851,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,22 +869,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702569</v>
+        <v>127704994</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -943,17 +924,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495103</v>
+        <v>494916</v>
       </c>
       <c r="R4" t="n">
-        <v>6720644</v>
+        <v>6720685</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,9 +961,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,49 +989,58 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702610</v>
+        <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495089</v>
+        <v>495103</v>
       </c>
       <c r="R5" t="n">
-        <v>6720547</v>
+        <v>6720644</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,37 +1111,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702618</v>
+        <v>127702557</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495091</v>
+        <v>495092</v>
       </c>
       <c r="R6" t="n">
-        <v>6720516</v>
+        <v>6720647</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1212,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702677</v>
+        <v>127702451</v>
       </c>
       <c r="B7" t="n">
-        <v>56864</v>
+        <v>98388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,31 +1232,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495011</v>
+        <v>494955</v>
       </c>
       <c r="R7" t="n">
-        <v>6720464</v>
+        <v>6720654</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1299,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,46 +1327,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702557</v>
+        <v>127702677</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495092</v>
+        <v>495011</v>
       </c>
       <c r="R8" t="n">
-        <v>6720647</v>
+        <v>6720464</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1408,7 +1414,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,42 +1432,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702451</v>
+        <v>127702618</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494955</v>
+        <v>495091</v>
       </c>
       <c r="R9" t="n">
-        <v>6720654</v>
+        <v>6720516</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702589</v>
+        <v>127702600</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495018</v>
+        <v>495093</v>
       </c>
       <c r="R13" t="n">
-        <v>6720585</v>
+        <v>6720552</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702600</v>
+        <v>127702589</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495093</v>
+        <v>495018</v>
       </c>
       <c r="R14" t="n">
-        <v>6720552</v>
+        <v>6720585</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702771</v>
+        <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,11 +2088,7 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2102,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494992</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>6720453</v>
+        <v>6720405</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2165,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702962</v>
+        <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2189,11 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494952</v>
+        <v>494992</v>
       </c>
       <c r="R16" t="n">
-        <v>6720405</v>
+        <v>6720453</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127702821</v>
+        <v>127702953</v>
       </c>
       <c r="B18" t="n">
-        <v>91349</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,24 +2386,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2413,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494992</v>
+        <v>494954</v>
       </c>
       <c r="R18" t="n">
-        <v>6720444</v>
+        <v>6720410</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2476,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,44 +2491,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R19" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,40 +2556,54 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127705132</v>
+        <v>127702821</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,45 +2611,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495088</v>
+        <v>494992</v>
       </c>
       <c r="R20" t="n">
-        <v>6720826</v>
+        <v>6720444</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,54 +2671,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702660</v>
+        <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,31 +2712,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495027</v>
+        <v>495000</v>
       </c>
       <c r="R21" t="n">
-        <v>6720505</v>
+        <v>6720439</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2788,6 +2783,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2806,7 +2802,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702665</v>
+        <v>127702660</v>
       </c>
       <c r="B22" t="n">
         <v>57669</v>
@@ -2839,7 +2835,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2849,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495093</v>
+        <v>495027</v>
       </c>
       <c r="R22" t="n">
-        <v>6720523</v>
+        <v>6720505</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2885,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,46 +2907,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127702665</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2963,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495093</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720523</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3001,13 +2988,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3026,37 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702866</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495000</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720439</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3127,37 +3127,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127703242</v>
+        <v>127702373</v>
       </c>
       <c r="B25" t="n">
-        <v>91645</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3165,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494910</v>
+        <v>494858</v>
       </c>
       <c r="R25" t="n">
-        <v>6720386</v>
+        <v>6720620</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3228,46 +3237,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127702373</v>
+        <v>127703242</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>91646</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494858</v>
+        <v>494910</v>
       </c>
       <c r="R26" t="n">
-        <v>6720620</v>
+        <v>6720386</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3442,7 +3442,7 @@
         <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,32 +3789,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702791</v>
+        <v>127702638</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3822,7 +3822,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495005</v>
+        <v>495058</v>
       </c>
       <c r="R31" t="n">
-        <v>6720454</v>
+        <v>6720525</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3868,11 +3868,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3899,32 +3894,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702638</v>
+        <v>127702791</v>
       </c>
       <c r="B32" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3932,7 +3927,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3942,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495058</v>
+        <v>495005</v>
       </c>
       <c r="R32" t="n">
-        <v>6720525</v>
+        <v>6720454</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3978,6 +3973,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,7 +4114,7 @@
         <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4322,55 +4322,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>92651</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R36" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4397,9 +4402,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,72 +4435,67 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>92652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R37" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4507,24 +4522,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -1111,46 +1111,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702557</v>
+        <v>127702618</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495092</v>
+        <v>495091</v>
       </c>
       <c r="R6" t="n">
-        <v>6720647</v>
+        <v>6720516</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1221,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702451</v>
+        <v>127702677</v>
       </c>
       <c r="B7" t="n">
-        <v>98388</v>
+        <v>56864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,31 +1223,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494955</v>
+        <v>495011</v>
       </c>
       <c r="R7" t="n">
-        <v>6720654</v>
+        <v>6720464</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702677</v>
+        <v>127702451</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>98388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,31 +1328,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495011</v>
+        <v>494955</v>
       </c>
       <c r="R8" t="n">
-        <v>6720464</v>
+        <v>6720654</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1414,6 +1404,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1432,37 +1423,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702618</v>
+        <v>127702557</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495091</v>
+        <v>495092</v>
       </c>
       <c r="R9" t="n">
-        <v>6720516</v>
+        <v>6720647</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1638,42 +1638,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1723,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1748,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,13 +1829,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,44 +2386,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R18" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,40 +2451,54 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127705132</v>
+        <v>127702821</v>
       </c>
       <c r="B19" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,45 +2506,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495088</v>
+        <v>494992</v>
       </c>
       <c r="R19" t="n">
-        <v>6720826</v>
+        <v>6720444</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2556,54 +2566,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127702821</v>
+        <v>127702953</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,24 +2607,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494992</v>
+        <v>494954</v>
       </c>
       <c r="R20" t="n">
-        <v>6720444</v>
+        <v>6720410</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702866</v>
+        <v>127702665</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,26 +2712,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495000</v>
+        <v>495093</v>
       </c>
       <c r="R21" t="n">
-        <v>6720439</v>
+        <v>6720523</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2777,13 +2782,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2907,42 +2916,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702665</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2950,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495093</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720523</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2988,17 +3001,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,46 +3026,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3338,37 +3338,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702579</v>
+        <v>127702385</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3376,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495079</v>
+        <v>494878</v>
       </c>
       <c r="R27" t="n">
-        <v>6720624</v>
+        <v>6720648</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3439,7 +3448,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127702385</v>
+        <v>127704897</v>
       </c>
       <c r="B28" t="n">
         <v>98468</v>
@@ -3469,7 +3478,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3482,17 +3491,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494878</v>
+        <v>494861</v>
       </c>
       <c r="R28" t="n">
-        <v>6720648</v>
+        <v>6720679</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3519,9 +3528,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,19 +3556,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127704897</v>
+        <v>127705446</v>
       </c>
       <c r="B29" t="n">
         <v>98468</v>
@@ -3579,7 +3598,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3596,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494861</v>
+        <v>494939</v>
       </c>
       <c r="R29" t="n">
-        <v>6720679</v>
+        <v>6720421</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3641,7 +3660,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,60 +3688,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127705446</v>
+        <v>127702579</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494939</v>
+        <v>495079</v>
       </c>
       <c r="R30" t="n">
-        <v>6720421</v>
+        <v>6720624</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,19 +3759,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4322,60 +4322,55 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>92652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R36" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4402,24 +4397,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,67 +4415,72 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B37" t="n">
-        <v>92652</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R37" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4522,9 +4507,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127704994</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,38 +1317,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702451</v>
+        <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>98388</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1360,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494955</v>
+        <v>495092</v>
       </c>
       <c r="R8" t="n">
-        <v>6720654</v>
+        <v>6720647</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1423,42 +1427,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702557</v>
+        <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495092</v>
+        <v>494955</v>
       </c>
       <c r="R9" t="n">
-        <v>6720647</v>
+        <v>6720654</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702600</v>
+        <v>127702589</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495093</v>
+        <v>495018</v>
       </c>
       <c r="R13" t="n">
-        <v>6720552</v>
+        <v>6720585</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702589</v>
+        <v>127702600</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495018</v>
+        <v>495093</v>
       </c>
       <c r="R14" t="n">
-        <v>6720585</v>
+        <v>6720552</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,37 +2060,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B15" t="n">
-        <v>91646</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2142,7 +2151,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2164,7 +2172,7 @@
         <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,46 +2274,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>91647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2356,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127705132</v>
+        <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>91351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,45 +2386,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495088</v>
+        <v>494992</v>
       </c>
       <c r="R18" t="n">
-        <v>6720826</v>
+        <v>6720444</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,54 +2446,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702821</v>
+        <v>127705132</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,40 +2487,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494992</v>
+        <v>495088</v>
       </c>
       <c r="R19" t="n">
-        <v>6720444</v>
+        <v>6720826</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2566,30 +2552,44 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2599,7 +2599,7 @@
         <v>127702953</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,42 +2701,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702665</v>
+        <v>127702485</v>
       </c>
       <c r="B21" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2744,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495093</v>
+        <v>495079</v>
       </c>
       <c r="R21" t="n">
-        <v>6720523</v>
+        <v>6720777</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2782,17 +2786,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702660</v>
+        <v>127702866</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>91351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,31 +2822,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495027</v>
+        <v>495000</v>
       </c>
       <c r="R22" t="n">
-        <v>6720505</v>
+        <v>6720439</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2898,6 +2893,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2916,46 +2912,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127702665</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2963,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495093</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720523</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3001,13 +2993,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3026,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702866</v>
+        <v>127702660</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,26 +3033,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3065,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495000</v>
+        <v>495027</v>
       </c>
       <c r="R24" t="n">
-        <v>6720439</v>
+        <v>6720505</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3108,7 +3109,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3127,46 +3127,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127702373</v>
+        <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>91647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3174,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494858</v>
+        <v>494910</v>
       </c>
       <c r="R25" t="n">
-        <v>6720620</v>
+        <v>6720386</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3237,37 +3228,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127703242</v>
+        <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>91646</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494910</v>
+        <v>494858</v>
       </c>
       <c r="R26" t="n">
-        <v>6720386</v>
+        <v>6720620</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3341,7 +3341,7 @@
         <v>127702385</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>127704897</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>127705446</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B31" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,29 +3800,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3832,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R31" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3876,6 +3877,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4015,30 +4017,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4048,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R33" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4092,7 +4093,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>127703039</v>
       </c>
       <c r="B36" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>127704958</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127704994</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98389</v>
+        <v>98390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702589</v>
+        <v>127702600</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495018</v>
+        <v>495093</v>
       </c>
       <c r="R13" t="n">
-        <v>6720585</v>
+        <v>6720552</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702600</v>
+        <v>127702589</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495093</v>
+        <v>495018</v>
       </c>
       <c r="R14" t="n">
-        <v>6720552</v>
+        <v>6720585</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,46 +2060,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>91648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2151,6 +2142,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2172,7 +2164,7 @@
         <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,37 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91647</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127705132</v>
+        <v>127702953</v>
       </c>
       <c r="B19" t="n">
-        <v>57669</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,45 +2487,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495088</v>
+        <v>494954</v>
       </c>
       <c r="R19" t="n">
-        <v>6720826</v>
+        <v>6720410</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2552,54 +2551,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B20" t="n">
-        <v>91371</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,44 +2592,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R20" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,76 +2657,81 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>91352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2748,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R21" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2811,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702866</v>
+        <v>127702665</v>
       </c>
       <c r="B22" t="n">
-        <v>91351</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,26 +2813,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2849,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495000</v>
+        <v>495093</v>
       </c>
       <c r="R22" t="n">
-        <v>6720439</v>
+        <v>6720523</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2887,13 +2883,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702665</v>
+        <v>127702660</v>
       </c>
       <c r="B23" t="n">
         <v>57669</v>
@@ -2945,7 +2945,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495093</v>
+        <v>495027</v>
       </c>
       <c r="R23" t="n">
-        <v>6720523</v>
+        <v>6720505</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2991,11 +2991,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,42 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702660</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3065,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495027</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720505</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3109,6 +3108,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,46 +3338,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702385</v>
+        <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3385,10 +3376,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494878</v>
+        <v>495079</v>
       </c>
       <c r="R27" t="n">
-        <v>6720648</v>
+        <v>6720624</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3448,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127704897</v>
+        <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,7 +3469,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3491,17 +3482,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494861</v>
+        <v>494878</v>
       </c>
       <c r="R28" t="n">
-        <v>6720679</v>
+        <v>6720648</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3528,19 +3519,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3556,22 +3537,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127705446</v>
+        <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3579,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3615,10 +3596,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494939</v>
+        <v>494861</v>
       </c>
       <c r="R29" t="n">
-        <v>6720421</v>
+        <v>6720679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,7 +3631,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3660,7 +3641,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,51 +3669,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127702579</v>
+        <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495079</v>
+        <v>494939</v>
       </c>
       <c r="R30" t="n">
-        <v>6720624</v>
+        <v>6720421</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,9 +3749,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,53 +3777,52 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702400</v>
+        <v>127702791</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3833,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494929</v>
+        <v>495005</v>
       </c>
       <c r="R31" t="n">
-        <v>6720649</v>
+        <v>6720454</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3871,13 +3870,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3896,32 +3899,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702791</v>
+        <v>127702638</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,7 +3932,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3939,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495005</v>
+        <v>495058</v>
       </c>
       <c r="R32" t="n">
-        <v>6720454</v>
+        <v>6720525</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3975,11 +3978,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B33" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,29 +4015,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4049,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R33" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4093,6 +4092,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>127703039</v>
       </c>
       <c r="B36" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>127704958</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>127702407</v>
       </c>
       <c r="B39" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>127702380</v>
       </c>
       <c r="B40" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -1111,37 +1111,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702618</v>
+        <v>127702451</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495091</v>
+        <v>494955</v>
       </c>
       <c r="R6" t="n">
-        <v>6720516</v>
+        <v>6720654</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1212,42 +1217,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702677</v>
+        <v>127702557</v>
       </c>
       <c r="B7" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495011</v>
+        <v>495092</v>
       </c>
       <c r="R7" t="n">
-        <v>6720464</v>
+        <v>6720647</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1299,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,46 +1327,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702557</v>
+        <v>127702618</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495092</v>
+        <v>495091</v>
       </c>
       <c r="R8" t="n">
-        <v>6720647</v>
+        <v>6720516</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1427,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702451</v>
+        <v>127702677</v>
       </c>
       <c r="B9" t="n">
-        <v>98390</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,31 +1439,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494955</v>
+        <v>495011</v>
       </c>
       <c r="R9" t="n">
-        <v>6720654</v>
+        <v>6720464</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1514,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1638,42 +1638,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1723,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1748,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,13 +1829,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2060,37 +2060,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B15" t="n">
-        <v>91648</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2142,7 +2151,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2161,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702771</v>
+        <v>127702962</v>
       </c>
       <c r="B16" t="n">
         <v>91648</v>
@@ -2189,11 +2197,7 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494992</v>
+        <v>494952</v>
       </c>
       <c r="R16" t="n">
-        <v>6720453</v>
+        <v>6720405</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2266,46 +2270,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702771</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>91648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>494992</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720453</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2356,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702866</v>
+        <v>127702665</v>
       </c>
       <c r="B21" t="n">
-        <v>91352</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,26 +2712,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495000</v>
+        <v>495093</v>
       </c>
       <c r="R21" t="n">
-        <v>6720439</v>
+        <v>6720523</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2777,13 +2782,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2802,7 +2811,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702665</v>
+        <v>127702660</v>
       </c>
       <c r="B22" t="n">
         <v>57669</v>
@@ -2835,7 +2844,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2845,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495093</v>
+        <v>495027</v>
       </c>
       <c r="R22" t="n">
-        <v>6720523</v>
+        <v>6720505</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2881,11 +2890,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,42 +2916,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702660</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2955,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495027</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720505</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2999,6 +3007,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,46 +3026,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3338,37 +3338,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702579</v>
+        <v>127702385</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3376,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495079</v>
+        <v>494878</v>
       </c>
       <c r="R27" t="n">
-        <v>6720624</v>
+        <v>6720648</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3439,7 +3448,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127702385</v>
+        <v>127704897</v>
       </c>
       <c r="B28" t="n">
         <v>98470</v>
@@ -3469,7 +3478,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3482,17 +3491,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494878</v>
+        <v>494861</v>
       </c>
       <c r="R28" t="n">
-        <v>6720648</v>
+        <v>6720679</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3519,9 +3528,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,19 +3556,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127704897</v>
+        <v>127705446</v>
       </c>
       <c r="B29" t="n">
         <v>98470</v>
@@ -3579,7 +3598,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3596,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494861</v>
+        <v>494939</v>
       </c>
       <c r="R29" t="n">
-        <v>6720679</v>
+        <v>6720421</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3641,7 +3660,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,60 +3688,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127705446</v>
+        <v>127702579</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494939</v>
+        <v>495079</v>
       </c>
       <c r="R30" t="n">
-        <v>6720421</v>
+        <v>6720624</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,19 +3759,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127703223</v>
+        <v>127702940</v>
       </c>
       <c r="B34" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4122,26 +4122,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4149,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494911</v>
+        <v>494952</v>
       </c>
       <c r="R34" t="n">
-        <v>6720390</v>
+        <v>6720414</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4179,12 +4184,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4193,7 +4203,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4212,10 +4221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127702940</v>
+        <v>127703223</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4223,31 +4232,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4255,10 +4259,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494952</v>
+        <v>494911</v>
       </c>
       <c r="R35" t="n">
-        <v>6720414</v>
+        <v>6720390</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4285,17 +4289,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,6 +4303,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4322,55 +4322,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>92654</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R36" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4397,9 +4402,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,72 +4435,67 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>92654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R37" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4507,24 +4522,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -780,51 +780,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702610</v>
+        <v>127704994</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495089</v>
+        <v>494916</v>
       </c>
       <c r="R3" t="n">
-        <v>6720547</v>
+        <v>6720685</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,9 +860,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,19 +888,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704994</v>
+        <v>127702569</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -911,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -924,17 +943,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494916</v>
+        <v>495103</v>
       </c>
       <c r="R4" t="n">
-        <v>6720685</v>
+        <v>6720644</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +980,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,58 +998,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702569</v>
+        <v>127702610</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495103</v>
+        <v>495089</v>
       </c>
       <c r="R5" t="n">
-        <v>6720644</v>
+        <v>6720547</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -780,60 +780,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R3" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +851,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,19 +869,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702569</v>
+        <v>127704994</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -930,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -943,17 +924,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495103</v>
+        <v>494916</v>
       </c>
       <c r="R4" t="n">
-        <v>6720644</v>
+        <v>6720685</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,9 +961,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,49 +989,58 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702610</v>
+        <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495089</v>
+        <v>495103</v>
       </c>
       <c r="R5" t="n">
-        <v>6720547</v>
+        <v>6720644</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2916,46 +2916,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2963,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3026,37 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702866</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495000</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720439</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B32" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,29 +3910,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3942,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R32" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3986,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4015,30 +4017,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4048,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R33" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4092,7 +4093,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -780,51 +780,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702610</v>
+        <v>127704994</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495089</v>
+        <v>494916</v>
       </c>
       <c r="R3" t="n">
-        <v>6720547</v>
+        <v>6720685</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,9 +860,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,19 +888,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704994</v>
+        <v>127702569</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -911,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -924,17 +943,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494916</v>
+        <v>495103</v>
       </c>
       <c r="R4" t="n">
-        <v>6720685</v>
+        <v>6720644</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +980,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,58 +998,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702569</v>
+        <v>127702610</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495103</v>
+        <v>495089</v>
       </c>
       <c r="R5" t="n">
-        <v>6720644</v>
+        <v>6720547</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -2060,46 +2060,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>91648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2151,6 +2142,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2169,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702962</v>
+        <v>127702771</v>
       </c>
       <c r="B16" t="n">
         <v>91648</v>
@@ -2197,7 +2189,11 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2207,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494952</v>
+        <v>494992</v>
       </c>
       <c r="R16" t="n">
-        <v>6720405</v>
+        <v>6720453</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2270,41 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702771</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91648</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494992</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720453</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2916,37 +2916,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702866</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2954,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495000</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720439</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3017,46 +3026,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,30 +3910,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3943,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R32" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3987,7 +3986,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4006,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B33" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,29 +4015,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4049,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R33" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4093,6 +4092,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -780,60 +780,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R3" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +851,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,19 +869,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702569</v>
+        <v>127704994</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -930,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -943,17 +924,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495103</v>
+        <v>494916</v>
       </c>
       <c r="R4" t="n">
-        <v>6720644</v>
+        <v>6720685</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,9 +961,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,49 +989,58 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702610</v>
+        <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495089</v>
+        <v>495103</v>
       </c>
       <c r="R5" t="n">
-        <v>6720547</v>
+        <v>6720644</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702451</v>
+        <v>127702677</v>
       </c>
       <c r="B6" t="n">
-        <v>98390</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,31 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494955</v>
+        <v>495011</v>
       </c>
       <c r="R6" t="n">
-        <v>6720654</v>
+        <v>6720464</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,7 +1198,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,42 +1216,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702557</v>
+        <v>127702451</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495092</v>
+        <v>494955</v>
       </c>
       <c r="R7" t="n">
-        <v>6720647</v>
+        <v>6720654</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1428,42 +1423,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702677</v>
+        <v>127702557</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495011</v>
+        <v>495092</v>
       </c>
       <c r="R9" t="n">
-        <v>6720464</v>
+        <v>6720647</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1515,6 +1514,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1638,42 +1638,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1723,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1748,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,13 +1829,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2060,37 +2060,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B15" t="n">
-        <v>91648</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2142,7 +2151,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2161,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702771</v>
+        <v>127702962</v>
       </c>
       <c r="B16" t="n">
         <v>91648</v>
@@ -2189,11 +2197,7 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494992</v>
+        <v>494952</v>
       </c>
       <c r="R16" t="n">
-        <v>6720453</v>
+        <v>6720405</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2266,46 +2270,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702771</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>91648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>494992</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720453</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2356,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2916,46 +2916,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2963,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3026,37 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702866</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495000</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720439</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3338,46 +3338,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702385</v>
+        <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3385,10 +3376,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494878</v>
+        <v>495079</v>
       </c>
       <c r="R27" t="n">
-        <v>6720648</v>
+        <v>6720624</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3448,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127704897</v>
+        <v>127702385</v>
       </c>
       <c r="B28" t="n">
         <v>98470</v>
@@ -3478,7 +3469,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3491,17 +3482,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494861</v>
+        <v>494878</v>
       </c>
       <c r="R28" t="n">
-        <v>6720679</v>
+        <v>6720648</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3528,19 +3519,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3556,19 +3537,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127705446</v>
+        <v>127704897</v>
       </c>
       <c r="B29" t="n">
         <v>98470</v>
@@ -3598,7 +3579,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3615,10 +3596,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494939</v>
+        <v>494861</v>
       </c>
       <c r="R29" t="n">
-        <v>6720421</v>
+        <v>6720679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,7 +3631,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3660,7 +3641,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,51 +3669,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127702579</v>
+        <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495079</v>
+        <v>494939</v>
       </c>
       <c r="R30" t="n">
-        <v>6720624</v>
+        <v>6720421</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,9 +3749,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B32" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,29 +3910,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3942,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R32" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3986,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4015,30 +4017,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4048,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R33" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4092,7 +4093,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2060,46 +2060,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>91648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2151,6 +2142,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2169,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702962</v>
+        <v>127702771</v>
       </c>
       <c r="B16" t="n">
         <v>91648</v>
@@ -2197,7 +2189,11 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2207,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494952</v>
+        <v>494992</v>
       </c>
       <c r="R16" t="n">
-        <v>6720405</v>
+        <v>6720453</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2270,41 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702771</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91648</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494992</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720453</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2916,37 +2916,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702866</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2954,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495000</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720439</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3017,46 +3026,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702866</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495000</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720439</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702677</v>
+        <v>127702451</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>98390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,31 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495011</v>
+        <v>494955</v>
       </c>
       <c r="R6" t="n">
-        <v>6720464</v>
+        <v>6720654</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,6 +1198,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,38 +1217,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702451</v>
+        <v>127702557</v>
       </c>
       <c r="B7" t="n">
-        <v>98390</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494955</v>
+        <v>495092</v>
       </c>
       <c r="R7" t="n">
-        <v>6720654</v>
+        <v>6720647</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1423,46 +1428,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702557</v>
+        <v>127702677</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495092</v>
+        <v>495011</v>
       </c>
       <c r="R9" t="n">
-        <v>6720647</v>
+        <v>6720464</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1514,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1638,42 +1638,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1723,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1748,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,13 +1829,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127704994</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127702569</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>127702451</v>
       </c>
       <c r="B6" t="n">
-        <v>98390</v>
+        <v>98398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,46 +1217,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702557</v>
+        <v>127702618</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495092</v>
+        <v>495091</v>
       </c>
       <c r="R7" t="n">
-        <v>6720647</v>
+        <v>6720516</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1327,37 +1318,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702618</v>
+        <v>127702677</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1365,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495091</v>
+        <v>495011</v>
       </c>
       <c r="R8" t="n">
-        <v>6720516</v>
+        <v>6720464</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1409,7 +1405,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1428,42 +1423,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702677</v>
+        <v>127702557</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495011</v>
+        <v>495092</v>
       </c>
       <c r="R9" t="n">
-        <v>6720464</v>
+        <v>6720647</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1515,6 +1514,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>127702475</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>127702327</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702600</v>
+        <v>127702589</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495093</v>
+        <v>495018</v>
       </c>
       <c r="R13" t="n">
-        <v>6720552</v>
+        <v>6720585</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702589</v>
+        <v>127702600</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495018</v>
+        <v>495093</v>
       </c>
       <c r="R14" t="n">
-        <v>6720585</v>
+        <v>6720552</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,37 +2060,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702501</v>
       </c>
       <c r="B15" t="n">
-        <v>91648</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>495076</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720763</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2142,7 +2151,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2161,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702771</v>
+        <v>127702962</v>
       </c>
       <c r="B16" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,11 +2197,7 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494992</v>
+        <v>494952</v>
       </c>
       <c r="R16" t="n">
-        <v>6720453</v>
+        <v>6720405</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2266,46 +2270,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702771</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>91656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>494992</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720453</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2356,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B19" t="n">
-        <v>91372</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,44 +2487,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R19" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,40 +2552,54 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127705132</v>
+        <v>127702953</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>91380</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,45 +2607,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495088</v>
+        <v>494954</v>
       </c>
       <c r="R20" t="n">
-        <v>6720826</v>
+        <v>6720410</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,44 +2671,30 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>127702665</v>
       </c>
       <c r="B21" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702660</v>
+        <v>127702866</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>91360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,31 +2822,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495027</v>
+        <v>495000</v>
       </c>
       <c r="R22" t="n">
-        <v>6720505</v>
+        <v>6720439</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2898,6 +2893,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2916,46 +2912,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127702660</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>57670</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2963,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495027</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720505</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3007,7 +2999,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3026,37 +3017,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702866</v>
+        <v>127702485</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495000</v>
+        <v>495079</v>
       </c>
       <c r="R24" t="n">
-        <v>6720439</v>
+        <v>6720777</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3130,7 +3130,7 @@
         <v>127703242</v>
       </c>
       <c r="B25" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127702373</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,40 +3789,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702791</v>
+        <v>127702400</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3832,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495005</v>
+        <v>494929</v>
       </c>
       <c r="R31" t="n">
-        <v>6720454</v>
+        <v>6720649</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3870,17 +3871,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3899,10 +3896,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,30 +3907,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3943,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R32" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3987,7 +3983,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4006,32 +4001,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702638</v>
+        <v>127702791</v>
       </c>
       <c r="B33" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4039,7 +4034,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4049,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495058</v>
+        <v>495005</v>
       </c>
       <c r="R33" t="n">
-        <v>6720525</v>
+        <v>6720454</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4085,6 +4080,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4111,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127702940</v>
+        <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>91360</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4122,31 +4122,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494952</v>
+        <v>494911</v>
       </c>
       <c r="R34" t="n">
-        <v>6720414</v>
+        <v>6720390</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4184,17 +4179,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,6 +4193,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4221,10 +4212,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127703223</v>
+        <v>127702940</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,26 +4223,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4259,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494911</v>
+        <v>494952</v>
       </c>
       <c r="R35" t="n">
-        <v>6720390</v>
+        <v>6720414</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4289,12 +4285,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>127704958</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>127703039</v>
       </c>
       <c r="B37" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127702407</v>
+        <v>127702380</v>
       </c>
       <c r="B39" t="n">
-        <v>91352</v>
+        <v>91325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494927</v>
+        <v>494869</v>
       </c>
       <c r="R39" t="n">
-        <v>6720666</v>
+        <v>6720629</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4758,32 +4758,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127702380</v>
+        <v>127702407</v>
       </c>
       <c r="B40" t="n">
-        <v>91317</v>
+        <v>91360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494869</v>
+        <v>494927</v>
       </c>
       <c r="R40" t="n">
-        <v>6720629</v>
+        <v>6720666</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4862,7 +4862,7 @@
         <v>127702522</v>
       </c>
       <c r="B41" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -780,51 +780,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702610</v>
+        <v>127704994</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495089</v>
+        <v>494916</v>
       </c>
       <c r="R3" t="n">
-        <v>6720547</v>
+        <v>6720685</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,9 +860,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,19 +888,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704994</v>
+        <v>127702569</v>
       </c>
       <c r="B4" t="n">
         <v>98478</v>
@@ -911,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -924,17 +943,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494916</v>
+        <v>495103</v>
       </c>
       <c r="R4" t="n">
-        <v>6720685</v>
+        <v>6720644</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +980,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,58 +998,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702569</v>
+        <v>127702610</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495103</v>
+        <v>495089</v>
       </c>
       <c r="R5" t="n">
-        <v>6720644</v>
+        <v>6720547</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1638,46 +1638,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702475</v>
+        <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495072</v>
+        <v>494819</v>
       </c>
       <c r="R11" t="n">
-        <v>6720807</v>
+        <v>6720617</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,13 +1719,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,42 +1748,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702327</v>
+        <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494819</v>
+        <v>495072</v>
       </c>
       <c r="R12" t="n">
-        <v>6720617</v>
+        <v>6720807</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1829,17 +1833,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2060,46 +2060,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702501</v>
+        <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>91656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495076</v>
+        <v>494952</v>
       </c>
       <c r="R15" t="n">
-        <v>6720763</v>
+        <v>6720405</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2151,6 +2142,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2169,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702962</v>
+        <v>127702771</v>
       </c>
       <c r="B16" t="n">
         <v>91656</v>
@@ -2197,7 +2189,11 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2207,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494952</v>
+        <v>494992</v>
       </c>
       <c r="R16" t="n">
-        <v>6720405</v>
+        <v>6720453</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2270,41 +2266,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702771</v>
+        <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>91656</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494992</v>
+        <v>495076</v>
       </c>
       <c r="R17" t="n">
-        <v>6720453</v>
+        <v>6720763</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2356,7 +2357,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127702821</v>
+        <v>127702953</v>
       </c>
       <c r="B18" t="n">
-        <v>91360</v>
+        <v>91380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,24 +2386,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2413,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494992</v>
+        <v>494954</v>
       </c>
       <c r="R18" t="n">
-        <v>6720444</v>
+        <v>6720410</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2476,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127705132</v>
+        <v>127702821</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>91360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,45 +2491,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495088</v>
+        <v>494992</v>
       </c>
       <c r="R19" t="n">
-        <v>6720826</v>
+        <v>6720444</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2552,54 +2551,40 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127702953</v>
+        <v>127705132</v>
       </c>
       <c r="B20" t="n">
-        <v>91380</v>
+        <v>57670</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,44 +2592,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494954</v>
+        <v>495088</v>
       </c>
       <c r="R20" t="n">
-        <v>6720410</v>
+        <v>6720826</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,40 +2657,54 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702665</v>
+        <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>57670</v>
+        <v>91360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,31 +2712,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495093</v>
+        <v>495000</v>
       </c>
       <c r="R21" t="n">
-        <v>6720523</v>
+        <v>6720439</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2782,17 +2777,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2811,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702866</v>
+        <v>127702660</v>
       </c>
       <c r="B22" t="n">
-        <v>91360</v>
+        <v>57670</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,26 +2813,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2849,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495000</v>
+        <v>495027</v>
       </c>
       <c r="R22" t="n">
-        <v>6720439</v>
+        <v>6720505</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2893,7 +2889,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2912,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702660</v>
+        <v>127702665</v>
       </c>
       <c r="B23" t="n">
         <v>57670</v>
@@ -2945,7 +2940,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495027</v>
+        <v>495093</v>
       </c>
       <c r="R23" t="n">
-        <v>6720505</v>
+        <v>6720523</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2991,6 +2986,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3896,32 +3896,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702638</v>
+        <v>127702791</v>
       </c>
       <c r="B32" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,7 +3929,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495058</v>
+        <v>495005</v>
       </c>
       <c r="R32" t="n">
-        <v>6720525</v>
+        <v>6720454</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3975,6 +3975,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4001,32 +4006,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702791</v>
+        <v>127702638</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4034,7 +4039,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4044,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495005</v>
+        <v>495058</v>
       </c>
       <c r="R33" t="n">
-        <v>6720454</v>
+        <v>6720525</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4080,11 +4085,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702466</v>
       </c>
       <c r="B2" t="n">
-        <v>92662</v>
+        <v>92673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,60 +780,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704994</v>
+        <v>127702610</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494916</v>
+        <v>495089</v>
       </c>
       <c r="R3" t="n">
-        <v>6720685</v>
+        <v>6720547</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +851,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,12 +869,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -903,7 +884,7 @@
         <v>127702569</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,51 +991,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127702610</v>
+        <v>127704994</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>98490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495089</v>
+        <v>494916</v>
       </c>
       <c r="R5" t="n">
-        <v>6720547</v>
+        <v>6720685</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1071,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702451</v>
+        <v>127702677</v>
       </c>
       <c r="B6" t="n">
-        <v>98398</v>
+        <v>56875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,31 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494955</v>
+        <v>495011</v>
       </c>
       <c r="R6" t="n">
-        <v>6720654</v>
+        <v>6720464</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,7 +1198,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>127702618</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,42 +1317,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702677</v>
+        <v>127702557</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>98490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495011</v>
+        <v>495092</v>
       </c>
       <c r="R8" t="n">
-        <v>6720464</v>
+        <v>6720647</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1405,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1423,42 +1427,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702557</v>
+        <v>127702451</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495092</v>
+        <v>494955</v>
       </c>
       <c r="R9" t="n">
-        <v>6720647</v>
+        <v>6720654</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1536,7 +1536,7 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92662</v>
+        <v>92673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>127702327</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>127702475</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702589</v>
+        <v>127702600</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495018</v>
+        <v>495093</v>
       </c>
       <c r="R13" t="n">
-        <v>6720585</v>
+        <v>6720552</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702600</v>
+        <v>127702589</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495093</v>
+        <v>495018</v>
       </c>
       <c r="R14" t="n">
-        <v>6720552</v>
+        <v>6720585</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2063,7 +2063,7 @@
         <v>127702962</v>
       </c>
       <c r="B15" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127702771</v>
       </c>
       <c r="B16" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>127702501</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127702953</v>
+        <v>127702821</v>
       </c>
       <c r="B18" t="n">
-        <v>91380</v>
+        <v>91371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,28 +2386,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2417,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494954</v>
+        <v>494992</v>
       </c>
       <c r="R18" t="n">
-        <v>6720410</v>
+        <v>6720444</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2480,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702821</v>
+        <v>127702953</v>
       </c>
       <c r="B19" t="n">
-        <v>91360</v>
+        <v>91391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,24 +2487,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494992</v>
+        <v>494954</v>
       </c>
       <c r="R19" t="n">
-        <v>6720444</v>
+        <v>6720410</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2584,7 +2584,7 @@
         <v>127705132</v>
       </c>
       <c r="B20" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>127702866</v>
       </c>
       <c r="B21" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127702660</v>
       </c>
       <c r="B22" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,42 +2907,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702665</v>
+        <v>127702485</v>
       </c>
       <c r="B23" t="n">
-        <v>57670</v>
+        <v>98490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2950,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495093</v>
+        <v>495079</v>
       </c>
       <c r="R23" t="n">
-        <v>6720523</v>
+        <v>6720777</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2988,17 +2992,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran från födosök.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,46 +3017,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702485</v>
+        <v>127702665</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>57681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495079</v>
+        <v>495093</v>
       </c>
       <c r="R24" t="n">
-        <v>6720777</v>
+        <v>6720523</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3102,13 +3098,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3127,37 +3127,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127703242</v>
+        <v>127702373</v>
       </c>
       <c r="B25" t="n">
-        <v>91656</v>
+        <v>98490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3165,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494910</v>
+        <v>494858</v>
       </c>
       <c r="R25" t="n">
-        <v>6720386</v>
+        <v>6720620</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3228,46 +3237,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127702373</v>
+        <v>127703242</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>91667</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494858</v>
+        <v>494910</v>
       </c>
       <c r="R26" t="n">
-        <v>6720620</v>
+        <v>6720386</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3341,7 +3341,7 @@
         <v>127702579</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>127702385</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>127704897</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>127705446</v>
       </c>
       <c r="B30" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702400</v>
+        <v>127702638</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>56875</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,30 +3800,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3833,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494929</v>
+        <v>495058</v>
       </c>
       <c r="R31" t="n">
-        <v>6720649</v>
+        <v>6720525</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3877,7 +3876,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3899,7 +3897,7 @@
         <v>127702791</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702638</v>
+        <v>127702400</v>
       </c>
       <c r="B33" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,29 +4015,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4049,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495058</v>
+        <v>494929</v>
       </c>
       <c r="R33" t="n">
-        <v>6720525</v>
+        <v>6720649</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4093,6 +4092,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>127703223</v>
       </c>
       <c r="B34" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>127702940</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,60 +4322,55 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127704958</v>
+        <v>127703039</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>92673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494869</v>
+        <v>494950</v>
       </c>
       <c r="R36" t="n">
-        <v>6720687</v>
+        <v>6720397</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4402,24 +4397,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,67 +4415,72 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127703039</v>
+        <v>127704958</v>
       </c>
       <c r="B37" t="n">
-        <v>92662</v>
+        <v>98490</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494950</v>
+        <v>494869</v>
       </c>
       <c r="R37" t="n">
-        <v>6720397</v>
+        <v>6720687</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4522,9 +4507,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,12 +4540,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
         <v>127702575</v>
       </c>
       <c r="B38" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4657,37 +4657,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127702380</v>
+        <v>127702522</v>
       </c>
       <c r="B39" t="n">
-        <v>91325</v>
+        <v>98490</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4695,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494869</v>
+        <v>495097</v>
       </c>
       <c r="R39" t="n">
-        <v>6720629</v>
+        <v>6720656</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4761,7 +4770,7 @@
         <v>127702407</v>
       </c>
       <c r="B40" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4859,46 +4868,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127702522</v>
+        <v>127702380</v>
       </c>
       <c r="B41" t="n">
-        <v>98478</v>
+        <v>91336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495097</v>
+        <v>494869</v>
       </c>
       <c r="R41" t="n">
-        <v>6720656</v>
+        <v>6720629</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127702466</v>
+        <v>127702771</v>
       </c>
       <c r="B2" t="n">
-        <v>92673</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495071</v>
+        <v>494992</v>
       </c>
       <c r="R2" t="n">
-        <v>6720799</v>
+        <v>6720453</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702610</v>
+        <v>127702962</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495089</v>
+        <v>494952</v>
       </c>
       <c r="R3" t="n">
-        <v>6720547</v>
+        <v>6720405</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,46 +881,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702569</v>
+        <v>127703242</v>
       </c>
       <c r="B4" t="n">
-        <v>98490</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495103</v>
+        <v>494910</v>
       </c>
       <c r="R4" t="n">
-        <v>6720644</v>
+        <v>6720386</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -991,60 +982,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127704994</v>
+        <v>127702407</v>
       </c>
       <c r="B5" t="n">
-        <v>98490</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494916</v>
+        <v>494927</v>
       </c>
       <c r="R5" t="n">
-        <v>6720685</v>
+        <v>6720666</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1053,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,54 +1071,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702677</v>
+        <v>127702821</v>
       </c>
       <c r="B6" t="n">
-        <v>56875</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495011</v>
+        <v>494992</v>
       </c>
       <c r="R6" t="n">
-        <v>6720464</v>
+        <v>6720444</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702618</v>
+        <v>127702866</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495091</v>
+        <v>495000</v>
       </c>
       <c r="R7" t="n">
-        <v>6720516</v>
+        <v>6720439</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1317,46 +1285,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127702557</v>
+        <v>127703223</v>
       </c>
       <c r="B8" t="n">
-        <v>98490</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495092</v>
+        <v>494911</v>
       </c>
       <c r="R8" t="n">
-        <v>6720647</v>
+        <v>6720390</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1394,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,42 +1386,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127702451</v>
+        <v>127702575</v>
       </c>
       <c r="B9" t="n">
-        <v>98410</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494955</v>
+        <v>495084</v>
       </c>
       <c r="R9" t="n">
-        <v>6720654</v>
+        <v>6720638</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1536,11 +1494,11 @@
         <v>127702365</v>
       </c>
       <c r="B10" t="n">
-        <v>92673</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1638,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127702327</v>
+        <v>127702466</v>
       </c>
       <c r="B11" t="n">
-        <v>57684</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,31 +1607,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494819</v>
+        <v>495071</v>
       </c>
       <c r="R11" t="n">
-        <v>6720617</v>
+        <v>6720799</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1719,17 +1676,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,46 +1701,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127702475</v>
+        <v>127703039</v>
       </c>
       <c r="B12" t="n">
-        <v>98490</v>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495072</v>
+        <v>494950</v>
       </c>
       <c r="R12" t="n">
-        <v>6720807</v>
+        <v>6720397</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1858,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702600</v>
+        <v>127702953</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,24 +1817,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1896,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495093</v>
+        <v>494954</v>
       </c>
       <c r="R13" t="n">
-        <v>6720552</v>
+        <v>6720410</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1959,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127702589</v>
+        <v>127702380</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495018</v>
+        <v>494869</v>
       </c>
       <c r="R14" t="n">
-        <v>6720585</v>
+        <v>6720629</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127702962</v>
+        <v>127702579</v>
       </c>
       <c r="B15" t="n">
-        <v>91667</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494952</v>
+        <v>495079</v>
       </c>
       <c r="R15" t="n">
-        <v>6720405</v>
+        <v>6720624</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2161,39 +2113,35 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127702771</v>
+        <v>127702589</v>
       </c>
       <c r="B16" t="n">
-        <v>91667</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2203,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494992</v>
+        <v>495018</v>
       </c>
       <c r="R16" t="n">
-        <v>6720453</v>
+        <v>6720585</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2266,46 +2214,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127702501</v>
+        <v>127702600</v>
       </c>
       <c r="B17" t="n">
-        <v>56875</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495076</v>
+        <v>495093</v>
       </c>
       <c r="R17" t="n">
-        <v>6720763</v>
+        <v>6720552</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2357,6 +2296,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2375,32 +2315,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127702821</v>
+        <v>127702610</v>
       </c>
       <c r="B18" t="n">
-        <v>91371</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494992</v>
+        <v>495089</v>
       </c>
       <c r="R18" t="n">
-        <v>6720444</v>
+        <v>6720547</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2476,39 +2416,35 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127702953</v>
+        <v>127702618</v>
       </c>
       <c r="B19" t="n">
-        <v>91391</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2518,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494954</v>
+        <v>495091</v>
       </c>
       <c r="R19" t="n">
-        <v>6720410</v>
+        <v>6720516</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2581,14 +2517,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127705132</v>
+        <v>127702660</v>
       </c>
       <c r="B20" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2614,23 +2550,23 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495088</v>
+        <v>495027</v>
       </c>
       <c r="R20" t="n">
-        <v>6720826</v>
+        <v>6720505</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,24 +2593,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2689,49 +2610,54 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127702866</v>
+        <v>127702665</v>
       </c>
       <c r="B21" t="n">
-        <v>91371</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495000</v>
+        <v>495093</v>
       </c>
       <c r="R21" t="n">
-        <v>6720439</v>
+        <v>6720523</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2777,13 +2703,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran från födosök.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2802,14 +2732,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127702660</v>
+        <v>127705070</v>
       </c>
       <c r="B22" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2833,25 +2763,21 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495027</v>
+        <v>494990</v>
       </c>
       <c r="R22" t="n">
-        <v>6720505</v>
+        <v>6720739</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2878,9 +2804,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födohål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,72 +2836,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127702485</v>
+        <v>127705132</v>
       </c>
       <c r="B23" t="n">
-        <v>98490</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495079</v>
+        <v>495088</v>
       </c>
       <c r="R23" t="n">
-        <v>6720777</v>
+        <v>6720826</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2987,40 +2924,54 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127702665</v>
+        <v>127702327</v>
       </c>
       <c r="B24" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,16 +2979,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3060,10 +3011,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495093</v>
+        <v>494819</v>
       </c>
       <c r="R24" t="n">
-        <v>6720523</v>
+        <v>6720617</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3100,7 +3051,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hack nedtill på gran från födosök.</t>
+          <t>Ringhack i tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3127,46 +3078,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127702373</v>
+        <v>127702791</v>
       </c>
       <c r="B25" t="n">
-        <v>98490</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3174,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494858</v>
+        <v>495005</v>
       </c>
       <c r="R25" t="n">
-        <v>6720620</v>
+        <v>6720454</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3212,13 +3159,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3237,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127703242</v>
+        <v>127702940</v>
       </c>
       <c r="B26" t="n">
-        <v>91667</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,26 +3199,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3231,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494910</v>
+        <v>494952</v>
       </c>
       <c r="R26" t="n">
-        <v>6720386</v>
+        <v>6720414</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3313,13 +3269,17 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3338,37 +3298,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127702579</v>
+        <v>127702501</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3376,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495079</v>
+        <v>495076</v>
       </c>
       <c r="R27" t="n">
-        <v>6720624</v>
+        <v>6720763</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3420,7 +3389,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3439,46 +3407,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127702385</v>
+        <v>127702638</v>
       </c>
       <c r="B28" t="n">
-        <v>98490</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3486,10 +3450,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494878</v>
+        <v>495058</v>
       </c>
       <c r="R28" t="n">
-        <v>6720648</v>
+        <v>6720525</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3530,7 +3494,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3549,60 +3512,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127704897</v>
+        <v>127702677</v>
       </c>
       <c r="B29" t="n">
-        <v>98490</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494861</v>
+        <v>495011</v>
       </c>
       <c r="R29" t="n">
-        <v>6720679</v>
+        <v>6720464</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3629,100 +3588,86 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127705446</v>
+        <v>127702400</v>
       </c>
       <c r="B30" t="n">
-        <v>98490</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494939</v>
+        <v>494929</v>
       </c>
       <c r="R30" t="n">
-        <v>6720421</v>
+        <v>6720649</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,19 +3694,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,54 +3712,58 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127702638</v>
+        <v>127702373</v>
       </c>
       <c r="B31" t="n">
-        <v>56875</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3832,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495058</v>
+        <v>494858</v>
       </c>
       <c r="R31" t="n">
-        <v>6720525</v>
+        <v>6720620</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3876,6 +3815,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3894,42 +3834,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127702791</v>
+        <v>127702385</v>
       </c>
       <c r="B32" t="n">
-        <v>57684</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3937,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495005</v>
+        <v>494878</v>
       </c>
       <c r="R32" t="n">
-        <v>6720454</v>
+        <v>6720648</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3975,17 +3919,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4004,43 +3944,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127702400</v>
+        <v>127702475</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4048,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494929</v>
+        <v>495072</v>
       </c>
       <c r="R33" t="n">
-        <v>6720649</v>
+        <v>6720807</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4111,37 +4054,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127703223</v>
+        <v>127702485</v>
       </c>
       <c r="B34" t="n">
-        <v>91371</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4149,10 +4101,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494911</v>
+        <v>495079</v>
       </c>
       <c r="R34" t="n">
-        <v>6720390</v>
+        <v>6720777</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4179,12 +4131,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4212,42 +4164,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127702940</v>
+        <v>127702522</v>
       </c>
       <c r="B35" t="n">
-        <v>57684</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4255,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494952</v>
+        <v>495097</v>
       </c>
       <c r="R35" t="n">
-        <v>6720414</v>
+        <v>6720656</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4293,17 +4249,13 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bohål, 7 meter upp i döende tall (alldeles under tallticka). Bohålet runt 5 cm stort.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4322,41 +4274,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127703039</v>
+        <v>127702557</v>
       </c>
       <c r="B36" t="n">
-        <v>92673</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4364,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494950</v>
+        <v>495092</v>
       </c>
       <c r="R36" t="n">
-        <v>6720397</v>
+        <v>6720647</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4427,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127704958</v>
+        <v>127702569</v>
       </c>
       <c r="B37" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4457,7 +4414,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4470,17 +4427,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494869</v>
+        <v>495103</v>
       </c>
       <c r="R37" t="n">
-        <v>6720687</v>
+        <v>6720644</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4507,24 +4464,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,67 +4482,72 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127702575</v>
+        <v>127704897</v>
       </c>
       <c r="B38" t="n">
-        <v>92661</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495084</v>
+        <v>494861</v>
       </c>
       <c r="R38" t="n">
-        <v>6720638</v>
+        <v>6720679</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,9 +4574,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4645,22 +4602,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127702522</v>
+        <v>127704958</v>
       </c>
       <c r="B39" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4687,7 +4644,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4700,17 +4657,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495097</v>
+        <v>494869</v>
       </c>
       <c r="R39" t="n">
-        <v>6720656</v>
+        <v>6720687</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4737,9 +4694,24 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>några m stjälk</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4755,63 +4727,72 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127702407</v>
+        <v>127704974</v>
       </c>
       <c r="B40" t="n">
-        <v>91371</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494927</v>
+        <v>494877</v>
       </c>
       <c r="R40" t="n">
-        <v>6720666</v>
+        <v>6720695</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4838,9 +4819,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4856,63 +4847,72 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127702380</v>
+        <v>127704994</v>
       </c>
       <c r="B41" t="n">
-        <v>91336</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>skeberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494869</v>
+        <v>494916</v>
       </c>
       <c r="R41" t="n">
-        <v>6720629</v>
+        <v>6720685</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4939,9 +4939,19 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4957,15 +4967,241 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127705446</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>skeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>494939</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6720421</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127702451</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tosstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>494955</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6720654</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37044-2025 artfynd.xlsx
+++ b/artfynd/A 37044-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702771</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127703242</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702866</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127703223</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702575</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702365</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702466</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127703039</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702953</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702380</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702579</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702589</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2312,6 +2392,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702600</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702610</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2514,6 +2604,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702618</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702660</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702665</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2845,6 +2950,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127705070</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2965,6 +3075,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127705132</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3075,6 +3190,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702327</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3185,6 +3305,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702791</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3295,6 +3420,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702940</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3404,6 +3534,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702501</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,6 +3644,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702638</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3614,6 +3754,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702677</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3721,6 +3866,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702400</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3831,6 +3981,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702373</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3941,6 +4096,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702385</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4051,6 +4211,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702475</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702485</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4271,6 +4441,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702522</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4381,6 +4556,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702557</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4491,6 +4671,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702569</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4611,6 +4796,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127704897</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4736,6 +4926,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127704958</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4856,6 +5051,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127704974</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4976,6 +5176,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127704994</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5096,6 +5301,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127705446</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5202,8 +5412,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702451</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>